--- a/project_completion_rubric.csv.xlsx
+++ b/project_completion_rubric.csv.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eldva\Documents\github\easydata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C30B8540-66CF-45CD-BF0A-56C83FD82E92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3E1F3E77-1591-4179-9DA4-7EAE67F7B3F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{0A3CA88A-010B-451C-8D72-DCF2BD483CAF}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{D0B0AC1E-BADD-4DFA-AFB5-08BFCE227FBC}"/>
   </bookViews>
   <sheets>
     <sheet name="project_completion_rubric" sheetId="1" r:id="rId1"/>
@@ -450,7 +450,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="38">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -630,8 +630,38 @@
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.749992370372631"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="10">
+  <borders count="19">
     <border>
       <left/>
       <right/>
@@ -746,6 +776,141 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -791,8 +956,56 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="36" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="36" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="36" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1167,503 +1380,542 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4CBF904-9FE7-4576-BE41-BBB2F8F06D1D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AEBC34BF-80B4-4434-9371-B048EF142C9C}">
   <dimension ref="A1:I25"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="25.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="43.6640625" customWidth="1"/>
-    <col min="4" max="4" width="53.5546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="56.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.77734375" customWidth="1"/>
+    <col min="3" max="3" width="44" customWidth="1"/>
+    <col min="4" max="4" width="19" customWidth="1"/>
+    <col min="5" max="5" width="20.109375" customWidth="1"/>
+    <col min="6" max="6" width="11.33203125" customWidth="1"/>
+    <col min="7" max="7" width="17.33203125" customWidth="1"/>
+    <col min="8" max="8" width="9.6640625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="1" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="9" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+    </row>
+    <row r="2" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A2" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="D2" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="11" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+    </row>
+    <row r="3" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A3" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E3" t="s">
+      <c r="D3" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="11" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+    </row>
+    <row r="4" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A4" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E4" t="s">
+      <c r="D4" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="11" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+    </row>
+    <row r="5" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A5" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F5" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G5" t="s">
-        <v>8</v>
-      </c>
-      <c r="H5" t="s">
+      <c r="G5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H5" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+    <row r="6" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A6" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E6" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="F6" t="s">
+      <c r="F6" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="G6" t="s">
-        <v>8</v>
-      </c>
-      <c r="H6" t="s">
+      <c r="G6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H6" s="1" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+    <row r="7" spans="1:9" ht="54.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E7" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="F7" t="s">
+      <c r="F7" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="G7" t="s">
+      <c r="G7" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="H7" t="s">
-        <v>8</v>
-      </c>
-      <c r="I7" t="s">
+      <c r="H7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I7" s="1" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+    <row r="8" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A8" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="E8" t="s">
+      <c r="E8" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="F8" t="s">
-        <v>8</v>
-      </c>
-      <c r="G8" t="s">
+      <c r="F8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G8" s="1" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
+    <row r="9" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A9" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="D9" t="s">
-        <v>8</v>
-      </c>
-      <c r="E9" t="s">
+      <c r="D9" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" s="11" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
+    </row>
+    <row r="10" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A10" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="D10" t="s">
-        <v>8</v>
-      </c>
-      <c r="E10" t="s">
+      <c r="D10" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E10" s="11" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
+      <c r="F10" s="1"/>
+      <c r="G10" s="1"/>
+    </row>
+    <row r="11" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A11" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="D11" t="s">
-        <v>8</v>
-      </c>
-      <c r="E11" t="s">
+      <c r="D11" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E11" s="11" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
+    </row>
+    <row r="12" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A12" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C12" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="D12" t="s">
-        <v>8</v>
-      </c>
-      <c r="E12" t="s">
+      <c r="D12" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E12" s="11" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
+      <c r="F12" s="1"/>
+      <c r="G12" s="1"/>
+    </row>
+    <row r="13" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A13" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="D13" t="s">
-        <v>8</v>
-      </c>
-      <c r="E13" t="s">
+      <c r="D13" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E13" s="11" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
+    </row>
+    <row r="14" spans="1:9" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C14" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="D14" t="s">
-        <v>8</v>
-      </c>
-      <c r="E14" t="s">
+      <c r="D14" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="11" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
+      <c r="F14" s="1"/>
+      <c r="G14" s="1"/>
+    </row>
+    <row r="15" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A15" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C15" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="D15" t="s">
+      <c r="D15" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="E15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" t="s">
+      <c r="E15" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F15" s="1" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
+      <c r="G15" s="1"/>
+    </row>
+    <row r="16" spans="1:9" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A16" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C16" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="D16" t="s">
+      <c r="D16" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="E16" t="s">
-        <v>8</v>
-      </c>
-      <c r="F16" t="s">
+      <c r="E16" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F16" s="1" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
+      <c r="G16" s="1"/>
+    </row>
+    <row r="17" spans="1:8" ht="72" x14ac:dyDescent="0.3">
+      <c r="A17" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C17" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="D17" t="s">
+      <c r="D17" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="E17" t="s">
+      <c r="E17" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="F17" t="s">
-        <v>8</v>
-      </c>
-      <c r="G17" t="s">
+      <c r="F17" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G17" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
+    <row r="18" spans="1:8" ht="72" x14ac:dyDescent="0.3">
+      <c r="A18" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C18" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="D18" t="s">
-        <v>8</v>
-      </c>
-      <c r="E18" t="s">
+      <c r="D18" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E18" s="11" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
+      <c r="F18" s="1"/>
+      <c r="G18" s="1"/>
+    </row>
+    <row r="19" spans="1:8" ht="72" x14ac:dyDescent="0.3">
+      <c r="A19" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C19" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="D19" t="s">
-        <v>8</v>
-      </c>
-      <c r="E19" t="s">
+      <c r="D19" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E19" s="11" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
+      <c r="F19" s="1"/>
+      <c r="G19" s="1"/>
+    </row>
+    <row r="20" spans="1:8" ht="71.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C20" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="D20" t="s">
+      <c r="D20" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="E20" t="s">
-        <v>8</v>
-      </c>
-      <c r="F20" t="s">
+      <c r="E20" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" s="1" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
+      <c r="G20" s="1"/>
+    </row>
+    <row r="21" spans="1:8" ht="72" x14ac:dyDescent="0.3">
+      <c r="A21" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C21" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="D21" t="s">
-        <v>8</v>
-      </c>
-      <c r="E21" t="s">
+      <c r="D21" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E21" s="11" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
+      <c r="F21" s="1"/>
+      <c r="G21" s="1"/>
+    </row>
+    <row r="22" spans="1:8" ht="72" x14ac:dyDescent="0.3">
+      <c r="A22" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C22" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="D22" t="s">
-        <v>8</v>
-      </c>
-      <c r="E22" t="s">
+      <c r="D22" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E22" s="11" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
+      <c r="F22" s="1"/>
+      <c r="G22" s="1"/>
+    </row>
+    <row r="23" spans="1:8" ht="72" x14ac:dyDescent="0.3">
+      <c r="A23" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C23" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="D23" t="s">
+      <c r="D23" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="E23" t="s">
+      <c r="E23" s="11" t="s">
         <v>87</v>
       </c>
-      <c r="F23" t="s">
+      <c r="F23" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="G23" t="s">
-        <v>8</v>
-      </c>
-      <c r="H23" t="s">
+      <c r="G23" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H23" s="1" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
+    <row r="24" spans="1:8" ht="72" x14ac:dyDescent="0.3">
+      <c r="A24" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="C24" t="s">
+      <c r="C24" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="D24" t="s">
-        <v>8</v>
-      </c>
-      <c r="E24" t="s">
+      <c r="D24" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E24" s="11" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
+      <c r="F24" s="1"/>
+      <c r="G24" s="1"/>
+    </row>
+    <row r="25" spans="1:8" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B25" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="C25" t="s">
+      <c r="C25" s="14" t="s">
         <v>94</v>
       </c>
-      <c r="D25" t="s">
-        <v>8</v>
-      </c>
-      <c r="E25" t="s">
+      <c r="D25" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="E25" s="16" t="s">
         <v>95</v>
       </c>
+      <c r="F25" s="1"/>
+      <c r="G25" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/project_completion_rubric.csv.xlsx
+++ b/project_completion_rubric.csv.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eldva\Documents\github\easydata\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eldva\Documents\GitHub\EasyData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3E1F3E77-1591-4179-9DA4-7EAE67F7B3F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{55B74AB3-4447-43E8-8188-AAFEBD9013FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{D0B0AC1E-BADD-4DFA-AFB5-08BFCE227FBC}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{BBBA40FD-F926-4DEF-A062-4F9BAA8B94A8}"/>
   </bookViews>
   <sheets>
     <sheet name="project_completion_rubric" sheetId="1" r:id="rId1"/>
@@ -20,294 +20,114 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="96">
-  <si>
-    <t>Phase</t>
-  </si>
-  <si>
-    <t>Requirement</t>
-  </si>
-  <si>
-    <t>Implementation Details</t>
-  </si>
-  <si>
-    <t>Status / Level</t>
-  </si>
-  <si>
-    <t>Source Code &amp; References</t>
-  </si>
-  <si>
-    <t>Phase 1: Foundation</t>
-  </si>
-  <si>
-    <t>Core API &amp; Express Setup</t>
-  </si>
-  <si>
-    <t>Express server written in TypeScript utilizing TSX. Includes basic health checks.</t>
-  </si>
-  <si>
-    <t>Exemplary (Level 3)</t>
-  </si>
-  <si>
-    <t>src/server.ts</t>
-  </si>
-  <si>
-    <t>Dynamic SQLite Backend</t>
-  </si>
-  <si>
-    <t>Dynamically loads and provisions a separate SQLite database file for each app inside the data folder.</t>
-  </si>
-  <si>
-    <t>src/services/app.service.ts</t>
-  </si>
-  <si>
-    <t>Token-Based Authentication</t>
-  </si>
-  <si>
-    <t>Protects app endpoints using Bearer Token authorization checking corresponding app metadata.</t>
-  </si>
-  <si>
-    <t>src/middleware/auth.middleware.ts</t>
-  </si>
-  <si>
-    <t>Schema &amp; Table Management</t>
-  </si>
-  <si>
-    <t>Allows creating tables dynamically and viewing schema structures with supported SQLite types (TEXT</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> INTEGER</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> REAL</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> BOOLEAN).</t>
-  </si>
-  <si>
-    <t>src/services/table.service.ts</t>
-  </si>
-  <si>
-    <t>Row CRUD Operations</t>
-  </si>
-  <si>
-    <t>Supports dynamic inserts</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> reads</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> updates</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> and deletes of rows.</t>
-  </si>
-  <si>
-    <t>src/routes/app.routes.ts</t>
-  </si>
-  <si>
-    <t>Query Parameters</t>
-  </si>
-  <si>
-    <t>Supports basic filtering</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ordering</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> and limiting through where</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> order</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> and limit URL query parameters.</t>
-  </si>
-  <si>
-    <t>Automated Testing</t>
-  </si>
-  <si>
-    <t>End-to-end integration tests using Vitest and Supertest checking auth</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> table schemas</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> and data insertion.</t>
-  </si>
-  <si>
-    <t>tests/app.test.ts</t>
-  </si>
-  <si>
-    <t>Phase 2: MCP Integration</t>
-  </si>
-  <si>
-    <t>MCP Server Setup</t>
-  </si>
-  <si>
-    <t>Utilizes @modelcontextprotocol/sdk to construct tools and schema definitions.</t>
-  </si>
-  <si>
-    <t>src/mcp/server.ts</t>
-  </si>
-  <si>
-    <t>Exposed MCP Tools</t>
-  </si>
-  <si>
-    <t>Exposes operations like create_app, get_schema, create_table, alter_table, insert_row, query_rows, update_row, delete_row, get_upload_url, and publish_app.</t>
-  </si>
-  <si>
-    <t>Stdio &amp; HTTP Transports</t>
-  </si>
-  <si>
-    <t>Supports stdio protocol for CLI integration and streamable HTTP server transport exposed at POST /mcp in Express.</t>
-  </si>
-  <si>
-    <t>src/server.ts &amp; src/mcp/server.ts</t>
-  </si>
-  <si>
-    <t>App Publishing Flow</t>
-  </si>
-  <si>
-    <t>Exposes functionality to upload and host single-page HTML applications generated by the AI assistant.</t>
-  </si>
-  <si>
-    <t>src/services/generated-app.service.ts</t>
-  </si>
-  <si>
-    <t>Phase 3: File Uploads</t>
-  </si>
-  <si>
-    <t>VPS Upload Endpoints</t>
-  </si>
-  <si>
-    <t>Implements standard multipart upload paths returning stable filenames and temporary signed views.</t>
-  </si>
-  <si>
-    <t>File Safety Enforcements</t>
-  </si>
-  <si>
-    <t>Sets limits of 5 MB per file and 50 MB total quota per app. Verifies MIME types and Magic Bytes to prevent malicious scripts.</t>
-  </si>
-  <si>
-    <t>src/middleware/upload.middleware.ts &amp; src/services/file.service.ts</t>
-  </si>
-  <si>
-    <t>Signed Expiring URLs</t>
-  </si>
-  <si>
-    <t>Secures files by only serving them using unique SHA-256 HMAC signed URLs that expire automatically (e.g.</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> after 1 hour).</t>
-  </si>
-  <si>
-    <t>src/services/file.service.ts</t>
-  </si>
-  <si>
-    <t>File/Row Cleanup</t>
-  </si>
-  <si>
-    <t>Automatically deletes associated files when a row referencing *_file_name is deleted</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> and purges all files upon app deletion.</t>
-  </si>
-  <si>
-    <t>src/services/app.service.ts &amp; src/services/table.service.ts</t>
-  </si>
-  <si>
-    <t>Phase 4: Security &amp; Guardrails</t>
-  </si>
-  <si>
-    <t>SQL Identifier Safety</t>
-  </si>
-  <si>
-    <t>Sanitizes and validates table names</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> column names</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> and query expressions to block SQL injection.</t>
-  </si>
-  <si>
-    <t>src/services/identifier.service.ts</t>
-  </si>
-  <si>
-    <t>Sensitive Schema Scan</t>
-  </si>
-  <si>
-    <t>Detects high-risk column patterns (e.g., kennitala, health, address, allergy) and returns dynamic API/MCP warnings.</t>
-  </si>
-  <si>
-    <t>src/services/sensitivity.service.ts</t>
-  </si>
-  <si>
-    <t>Confirm Sensitive Fields</t>
-  </si>
-  <si>
-    <t>Rejects creating schemas with sensitive fields unless explicitly confirmed using a confirmSensitiveData flag.</t>
-  </si>
-  <si>
-    <t>Data Retention Policies</t>
-  </si>
-  <si>
-    <t>New apps receive a default recommendation (e.g.</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> end of school year). Retention schedules can be updated or read.</t>
-  </si>
-  <si>
-    <t>Export Before Delete</t>
-  </si>
-  <si>
-    <t>Offers a backup API endpoint /apps/:id/export to retrieve data in a standard JSON schema format before purging.</t>
-  </si>
-  <si>
-    <t>Rate Limiting</t>
-  </si>
-  <si>
-    <t>Restricts repetitive API requests per IP address to safeguard server availability.</t>
-  </si>
-  <si>
-    <t>src/middleware/rate-limit.middleware.ts</t>
-  </si>
-  <si>
-    <t>Audit Logs</t>
-  </si>
-  <si>
-    <t>Tracks critical database administrative events (e.g.</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> app creation</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> deletions</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> schema modifications).</t>
-  </si>
-  <si>
-    <t>src/services/audit.service.ts</t>
-  </si>
-  <si>
-    <t>Teacher Compliance Guides</t>
-  </si>
-  <si>
-    <t>Detailed guides in English and Icelandic on classroom data hygiene and compliance (GDPR/FERPA).</t>
-  </si>
-  <si>
-    <t>docs/data-protection-guide.md &amp; docs/data-protection-guide.is.md</t>
-  </si>
-  <si>
-    <t>App Security Checks</t>
-  </si>
-  <si>
-    <t>Validates generated single-page app HTML inputs to prevent injection of public files or hardcoded admin tokens.</t>
-  </si>
-  <si>
-    <t>src/routes/ai.routes.ts</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>Grades 0 - 2</t>
+  </si>
+  <si>
+    <t>Grades 3 - 4</t>
+  </si>
+  <si>
+    <t>Grades 5 - 6</t>
+  </si>
+  <si>
+    <t>Grades 7 - 8</t>
+  </si>
+  <si>
+    <t>Grades 9 - 10</t>
+  </si>
+  <si>
+    <t>Technology stack</t>
+  </si>
+  <si>
+    <t>Technology stack is poorly defined, incomplete, or inappropriate for the project. Key essential files (e.g., package.json, configuration files) are missing or misconfigured, preventing execution.</t>
+  </si>
+  <si>
+    <t>The technology stack is partially functional but contains major gaps or misconfigurations (e.g., version mismatches, unused dependencies, or lack of logical structure). Implementation does not follow standard developer practices.</t>
+  </si>
+  <si>
+    <t>The technology stack is complete and functional, but lacks optimization. Basic tools and frameworks are correctly set up, though there are minor integration issues or redundant packages.</t>
+  </si>
+  <si>
+    <t>Solid and appropriate technology stack selection and setup. Dependencies are well-managed, configurations are clean and documented, and standard build/run scripts are fully functional.</t>
+  </si>
+  <si>
+    <t>Outstanding and robust technology stack setup. Highly optimized configuration (e.g., custom scripts, clean tsconfig, environment controls), clear folder structure, secure dependency management, and flawless build tooling.</t>
+  </si>
+  <si>
+    <t>Interactive demonstration</t>
+  </si>
+  <si>
+    <t>The application fails to run, crashes during the demonstration, or does not show any interactive core functionality. The demo is broken.</t>
+  </si>
+  <si>
+    <t>The application runs but is unstable. Core features fail under simple scenarios, or there are significant UI/UX bugs that disrupt the demonstration flow.</t>
+  </si>
+  <si>
+    <t>The demonstration successfully displays the main user flow and features. However, UI transitions are clunky, and some secondary features or edge cases do not work.</t>
+  </si>
+  <si>
+    <t>A smooth and stable demonstration. Core and secondary features are successfully showcased under standard use cases, with a responsive UI and minimal hiccups.</t>
+  </si>
+  <si>
+    <t>Flawless and engaging demonstration. All features, including advanced edge cases and error handling, are shown seamlessly. The UI is highly responsive with smooth animations and transitions.</t>
+  </si>
+  <si>
+    <t>Product overall</t>
+  </si>
+  <si>
+    <t>The final product is incomplete, broken, or fails to meet the fundamental project requirements. Gaps are extensive and critical.</t>
+  </si>
+  <si>
+    <t>The product is a basic functional prototype but lacks polish, responsiveness, or critical guardrails (e.g., security, error validation). User experience is poor.</t>
+  </si>
+  <si>
+    <t>The product meets all minimum requirements and is reasonably stable. However, the design is basic, and it lacks advanced features, premium aesthetics, or robust error handling.</t>
+  </si>
+  <si>
+    <t>A highly functional and polished product. Features are well-integrated, the application is secure, responsive, and reliable, providing a great overall user experience.</t>
+  </si>
+  <si>
+    <t>An exceptional, production-ready product. Features a premium design, responsive layouts, robust security check, high-performance optimization, and thoughtful UI/UX polish.</t>
+  </si>
+  <si>
+    <t>Presentation overall</t>
+  </si>
+  <si>
+    <t>The presentation is disorganized, poorly timed, and lacks structure. Materials are sparse, messy, or completely missing. Low engagement.</t>
+  </si>
+  <si>
+    <t>The presentation is structured but hard to follow or dry. Timing is poorly managed, and presentation slides/materials are cluttered or overly wordy.</t>
+  </si>
+  <si>
+    <t>A coherent presentation with a logical structure. The project requirements are covered, timing is acceptable, and visuals are clean but generic.</t>
+  </si>
+  <si>
+    <t>Professional and engaging presentation. Content is well-paced, slides/visuals are clean and high-quality, and the narrative flow clearly highlights project goals and achievements.</t>
+  </si>
+  <si>
+    <t>Masterful, visually stunning, and highly professional presentation. Pacing is perfect, delivery is engaging and confident, and the slides have premium aesthetics that wow the audience.</t>
+  </si>
+  <si>
+    <t>Answering questions</t>
+  </si>
+  <si>
+    <t>Cannot answer basic questions about the codebase, technology choices, or architecture, or gives defensive/incorrect answers.</t>
+  </si>
+  <si>
+    <t>Answers questions with hesitation or provides vague, surface-level explanations that show a weak grasp of the project's details.</t>
+  </si>
+  <si>
+    <t>Answers standard questions correctly but struggles to justify architectural decisions, trade-offs, or explain complex technical edge cases.</t>
+  </si>
+  <si>
+    <t>Confident and accurate responses to technical and architectural questions. Demonstrates a clear understanding of the codebase and justifications for design choices.</t>
+  </si>
+  <si>
+    <t>Demonstrates complete mastery. Answers all technical, architectural, and design questions with precision, authority, and deep analytical insight, showing absolute codebase ownership.</t>
   </si>
 </sst>
 </file>
@@ -450,7 +270,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="38">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -628,24 +448,6 @@
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.39997558519241921"/>
         <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
@@ -656,7 +458,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.749992370372631"/>
+        <fgColor theme="3" tint="0.89999084444715716"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -956,39 +764,27 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="35" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="36" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="34" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="35" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="36" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="37" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="37" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1000,10 +796,7 @@
     <xf numFmtId="0" fontId="0" fillId="35" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="36" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="37" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1380,542 +1173,139 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AEBC34BF-80B4-4434-9371-B048EF142C9C}">
-  <dimension ref="A1:I25"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5300376B-7AFF-4512-9871-85C243289977}">
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr defaultColWidth="23.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="24.77734375" customWidth="1"/>
-    <col min="3" max="3" width="44" customWidth="1"/>
-    <col min="4" max="4" width="19" customWidth="1"/>
-    <col min="5" max="5" width="20.109375" customWidth="1"/>
-    <col min="6" max="6" width="11.33203125" customWidth="1"/>
-    <col min="7" max="7" width="17.33203125" customWidth="1"/>
-    <col min="8" max="8" width="9.6640625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="8.88671875" style="1"/>
+    <col min="1" max="1" width="16.21875" customWidth="1"/>
+    <col min="2" max="2" width="37" customWidth="1"/>
+    <col min="3" max="3" width="41.6640625" customWidth="1"/>
+    <col min="4" max="4" width="33.88671875" customWidth="1"/>
+    <col min="5" max="5" width="36" customWidth="1"/>
+    <col min="6" max="6" width="40.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
+      <c r="F1" s="5" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="2" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A2" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" s="2" t="s">
+    <row r="2" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+      <c r="A2" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="C2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="11" t="s">
+      <c r="D2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
+      <c r="E2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="3" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A3" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E3" s="11" t="s">
+    <row r="3" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+      <c r="A3" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
+      <c r="B3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>17</v>
+      </c>
     </row>
-    <row r="4" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A4" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E4" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
+    <row r="4" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+      <c r="A4" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>23</v>
+      </c>
     </row>
-    <row r="5" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A5" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E5" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>21</v>
+    <row r="5" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+      <c r="A5" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A6" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="E6" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="54.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D7" s="4" t="s">
+    <row r="6" spans="1:6" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="E7" s="11" t="s">
+      <c r="B6" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="C6" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="G7" s="1" t="s">
+      <c r="D6" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="H7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A8" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="B8" s="2" t="s">
+      <c r="E6" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="F6" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="D8" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="E8" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E9" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
-    </row>
-    <row r="10" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E10" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
-    </row>
-    <row r="11" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A11" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E11" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="F11" s="1"/>
-      <c r="G11" s="1"/>
-    </row>
-    <row r="12" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A12" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E12" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="F12" s="1"/>
-      <c r="G12" s="1"/>
-    </row>
-    <row r="13" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A13" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E13" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="F13" s="1"/>
-      <c r="G13" s="1"/>
-    </row>
-    <row r="14" spans="1:9" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E14" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="F14" s="1"/>
-      <c r="G14" s="1"/>
-    </row>
-    <row r="15" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A15" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="E15" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="G15" s="1"/>
-    </row>
-    <row r="16" spans="1:9" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A16" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="E16" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="G16" s="1"/>
-    </row>
-    <row r="17" spans="1:8" ht="72" x14ac:dyDescent="0.3">
-      <c r="A17" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="E17" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G17" s="1" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" ht="72" x14ac:dyDescent="0.3">
-      <c r="A18" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E18" s="11" t="s">
-        <v>73</v>
-      </c>
-      <c r="F18" s="1"/>
-      <c r="G18" s="1"/>
-    </row>
-    <row r="19" spans="1:8" ht="72" x14ac:dyDescent="0.3">
-      <c r="A19" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E19" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="F19" s="1"/>
-      <c r="G19" s="1"/>
-    </row>
-    <row r="20" spans="1:8" ht="71.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="E20" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F20" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="G20" s="1"/>
-    </row>
-    <row r="21" spans="1:8" ht="72" x14ac:dyDescent="0.3">
-      <c r="A21" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E21" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="F21" s="1"/>
-      <c r="G21" s="1"/>
-    </row>
-    <row r="22" spans="1:8" ht="72" x14ac:dyDescent="0.3">
-      <c r="A22" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="D22" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E22" s="11" t="s">
-        <v>83</v>
-      </c>
-      <c r="F22" s="1"/>
-      <c r="G22" s="1"/>
-    </row>
-    <row r="23" spans="1:8" ht="72" x14ac:dyDescent="0.3">
-      <c r="A23" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="D23" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="E23" s="11" t="s">
-        <v>87</v>
-      </c>
-      <c r="F23" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="G23" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="H23" s="1" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" ht="72" x14ac:dyDescent="0.3">
-      <c r="A24" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="D24" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E24" s="11" t="s">
-        <v>92</v>
-      </c>
-      <c r="F24" s="1"/>
-      <c r="G24" s="1"/>
-    </row>
-    <row r="25" spans="1:8" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="B25" s="13" t="s">
-        <v>93</v>
-      </c>
-      <c r="C25" s="14" t="s">
-        <v>94</v>
-      </c>
-      <c r="D25" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="E25" s="16" t="s">
-        <v>95</v>
-      </c>
-      <c r="F25" s="1"/>
-      <c r="G25" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>